--- a/Source Data/Sensitivity_Analyses_source_data/LOO_LC_Cortex_Gradient.xlsx
+++ b/Source Data/Sensitivity_Analyses_source_data/LOO_LC_Cortex_Gradient.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studntnu-my.sharepoint.com/personal/arjunad_ntnu_no/Documents/Desktop/LC_Cortex Gradient/Revision2/Code_Github/Source Data/Sensitivity_Analyses_source_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studntnu-my.sharepoint.com/personal/arjunad_ntnu_no/Documents/Desktop/LC_Cortex Gradient/Revision2/Code_Github_Final/Source Data/Sensitivity_Analyses_source_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{898C9124-5C45-4E48-AC84-762FA3579711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{449F4952-1EA6-45FF-B24B-60D09891706A}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{898C9124-5C45-4E48-AC84-762FA3579711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4B32A7C-2113-4C67-B698-EDDF7C51A104}"/>
   <bookViews>
-    <workbookView xWindow="-32220" yWindow="4230" windowWidth="28800" windowHeight="15345" xr2:uid="{66EB4841-5220-44DD-9C48-545B8499B98A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{66EB4841-5220-44DD-9C48-545B8499B98A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="12">
   <si>
     <t>Right_G1_Negative</t>
   </si>
@@ -77,442 +76,15 @@
   <si>
     <t>Sub</t>
   </si>
-  <si>
-    <t>sub-11001</t>
-  </si>
-  <si>
-    <t>sub-11004</t>
-  </si>
-  <si>
-    <t>sub-11009</t>
-  </si>
-  <si>
-    <t>sub-11012</t>
-  </si>
-  <si>
-    <t>sub-11018</t>
-  </si>
-  <si>
-    <t>sub-11020</t>
-  </si>
-  <si>
-    <t>sub-11021</t>
-  </si>
-  <si>
-    <t>sub-11024</t>
-  </si>
-  <si>
-    <t>sub-11025</t>
-  </si>
-  <si>
-    <t>sub-11031</t>
-  </si>
-  <si>
-    <t>sub-11034</t>
-  </si>
-  <si>
-    <t>sub-11037</t>
-  </si>
-  <si>
-    <t>sub-11038</t>
-  </si>
-  <si>
-    <t>sub-11042</t>
-  </si>
-  <si>
-    <t>sub-11043</t>
-  </si>
-  <si>
-    <t>sub-11047</t>
-  </si>
-  <si>
-    <t>sub-11050</t>
-  </si>
-  <si>
-    <t>sub-11051</t>
-  </si>
-  <si>
-    <t>sub-11053</t>
-  </si>
-  <si>
-    <t>sub-11055</t>
-  </si>
-  <si>
-    <t>sub-11057</t>
-  </si>
-  <si>
-    <t>sub-11060</t>
-  </si>
-  <si>
-    <t>sub-11061</t>
-  </si>
-  <si>
-    <t>sub-11062</t>
-  </si>
-  <si>
-    <t>sub-11065</t>
-  </si>
-  <si>
-    <t>sub-11070</t>
-  </si>
-  <si>
-    <t>sub-11072</t>
-  </si>
-  <si>
-    <t>sub-11073</t>
-  </si>
-  <si>
-    <t>sub-11074</t>
-  </si>
-  <si>
-    <t>sub-11078</t>
-  </si>
-  <si>
-    <t>sub-11079</t>
-  </si>
-  <si>
-    <t>sub-11085</t>
-  </si>
-  <si>
-    <t>sub-11088</t>
-  </si>
-  <si>
-    <t>sub-11089</t>
-  </si>
-  <si>
-    <t>sub-11091</t>
-  </si>
-  <si>
-    <t>sub-11092</t>
-  </si>
-  <si>
-    <t>sub-11093</t>
-  </si>
-  <si>
-    <t>sub-11097</t>
-  </si>
-  <si>
-    <t>sub-11101</t>
-  </si>
-  <si>
-    <t>sub-11102</t>
-  </si>
-  <si>
-    <t>sub-11103</t>
-  </si>
-  <si>
-    <t>sub-11106</t>
-  </si>
-  <si>
-    <t>sub-11108</t>
-  </si>
-  <si>
-    <t>sub-11110</t>
-  </si>
-  <si>
-    <t>sub-11111</t>
-  </si>
-  <si>
-    <t>sub-11113</t>
-  </si>
-  <si>
-    <t>sub-11115</t>
-  </si>
-  <si>
-    <t>sub-11118</t>
-  </si>
-  <si>
-    <t>sub-11122</t>
-  </si>
-  <si>
-    <t>sub-11127</t>
-  </si>
-  <si>
-    <t>sub-11135</t>
-  </si>
-  <si>
-    <t>sub-11141</t>
-  </si>
-  <si>
-    <t>sub-11145</t>
-  </si>
-  <si>
-    <t>sub-11147</t>
-  </si>
-  <si>
-    <t>sub-11157</t>
-  </si>
-  <si>
-    <t>sub-11159</t>
-  </si>
-  <si>
-    <t>sub-11166</t>
-  </si>
-  <si>
-    <t>sub-11170</t>
-  </si>
-  <si>
-    <t>sub-11153</t>
-  </si>
-  <si>
-    <t>sub-11172</t>
-  </si>
-  <si>
-    <t>sub-11175</t>
-  </si>
-  <si>
-    <t>sub-11179</t>
-  </si>
-  <si>
-    <t>sub-11180</t>
-  </si>
-  <si>
-    <t>sub-11182</t>
-  </si>
-  <si>
-    <t>sub-11197</t>
-  </si>
-  <si>
-    <t>sub-11201</t>
-  </si>
-  <si>
-    <t>sub-11207</t>
-  </si>
-  <si>
-    <t>sub-11211</t>
-  </si>
-  <si>
-    <t>sub-11213</t>
-  </si>
-  <si>
-    <t>sub-11214</t>
-  </si>
-  <si>
-    <t>sub-11215</t>
-  </si>
-  <si>
-    <t>sub-11216</t>
-  </si>
-  <si>
-    <t>sub-12008</t>
-  </si>
-  <si>
-    <t>sub-12010</t>
-  </si>
-  <si>
-    <t>sub-12011</t>
-  </si>
-  <si>
-    <t>sub-12015</t>
-  </si>
-  <si>
-    <t>sub-12017</t>
-  </si>
-  <si>
-    <t>sub-12028</t>
-  </si>
-  <si>
-    <t>sub-12035</t>
-  </si>
-  <si>
-    <t>sub-12052</t>
-  </si>
-  <si>
-    <t>sub-12055</t>
-  </si>
-  <si>
-    <t>sub-12058</t>
-  </si>
-  <si>
-    <t>sub-12059</t>
-  </si>
-  <si>
-    <t>sub-12062</t>
-  </si>
-  <si>
-    <t>sub-12075</t>
-  </si>
-  <si>
-    <t>sub-12076</t>
-  </si>
-  <si>
-    <t>sub-12077</t>
-  </si>
-  <si>
-    <t>sub-12078</t>
-  </si>
-  <si>
-    <t>sub-12083</t>
-  </si>
-  <si>
-    <t>sub-12085</t>
-  </si>
-  <si>
-    <t>sub-12089</t>
-  </si>
-  <si>
-    <t>sub-12096</t>
-  </si>
-  <si>
-    <t>sub-12099</t>
-  </si>
-  <si>
-    <t>sub-12102</t>
-  </si>
-  <si>
-    <t>sub-12104</t>
-  </si>
-  <si>
-    <t>sub-12105</t>
-  </si>
-  <si>
-    <t>sub-12111</t>
-  </si>
-  <si>
-    <t>sub-12113</t>
-  </si>
-  <si>
-    <t>sub-12114</t>
-  </si>
-  <si>
-    <t>sub-12122</t>
-  </si>
-  <si>
-    <t>sub-12127</t>
-  </si>
-  <si>
-    <t>sub-12130</t>
-  </si>
-  <si>
-    <t>sub-12137</t>
-  </si>
-  <si>
-    <t>sub-12138</t>
-  </si>
-  <si>
-    <t>sub-12152</t>
-  </si>
-  <si>
-    <t>sub-12157</t>
-  </si>
-  <si>
-    <t>sub-12160</t>
-  </si>
-  <si>
-    <t>sub-12165</t>
-  </si>
-  <si>
-    <t>sub-12169</t>
-  </si>
-  <si>
-    <t>sub-12172</t>
-  </si>
-  <si>
-    <t>sub-12174</t>
-  </si>
-  <si>
-    <t>sub-12177</t>
-  </si>
-  <si>
-    <t>sub-12183</t>
-  </si>
-  <si>
-    <t>sub-12186</t>
-  </si>
-  <si>
-    <t>sub-12188</t>
-  </si>
-  <si>
-    <t>sub-12189</t>
-  </si>
-  <si>
-    <t>sub-12198</t>
-  </si>
-  <si>
-    <t>sub-12202</t>
-  </si>
-  <si>
-    <t>sub-12204</t>
-  </si>
-  <si>
-    <t>sub-12216</t>
-  </si>
-  <si>
-    <t>sub-12217</t>
-  </si>
-  <si>
-    <t>sub-12220</t>
-  </si>
-  <si>
-    <t>sub-12235</t>
-  </si>
-  <si>
-    <t>sub-12236</t>
-  </si>
-  <si>
-    <t>sub-12238</t>
-  </si>
-  <si>
-    <t>sub-12242</t>
-  </si>
-  <si>
-    <t>sub-12254</t>
-  </si>
-  <si>
-    <t>sub-12255</t>
-  </si>
-  <si>
-    <t>sub-12270</t>
-  </si>
-  <si>
-    <t>sub-12279</t>
-  </si>
-  <si>
-    <t>sub-12281</t>
-  </si>
-  <si>
-    <t>sub-12283</t>
-  </si>
-  <si>
-    <t>sub-12288</t>
-  </si>
-  <si>
-    <t>sub-12291</t>
-  </si>
-  <si>
-    <t>sub-12292</t>
-  </si>
-  <si>
-    <t>sub-12295</t>
-  </si>
-  <si>
-    <t>sub-12298</t>
-  </si>
-  <si>
-    <t>sub-12301</t>
-  </si>
-  <si>
-    <t>sub-12320</t>
-  </si>
-  <si>
-    <t>sub-12334</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -540,7 +112,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -911,8 +483,8 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
+      <c r="A2">
+        <v>11001</v>
       </c>
       <c r="B2">
         <v>0.219912147912148</v>
@@ -943,8 +515,8 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
+      <c r="A3">
+        <v>11004</v>
       </c>
       <c r="B3">
         <v>0.43693858093858101</v>
@@ -975,8 +547,8 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
+      <c r="A4">
+        <v>11009</v>
       </c>
       <c r="B4">
         <v>0.41480731880731903</v>
@@ -1007,8 +579,8 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
+      <c r="A5">
+        <v>11012</v>
       </c>
       <c r="B5">
         <v>0.45408469008468999</v>
@@ -1039,8 +611,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
+      <c r="A6">
+        <v>11018</v>
       </c>
       <c r="B6">
         <v>0.56567636567636603</v>
@@ -1071,8 +643,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
+      <c r="A7">
+        <v>11020</v>
       </c>
       <c r="B7">
         <v>0.34094143694143703</v>
@@ -1103,8 +675,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
+      <c r="A8">
+        <v>11021</v>
       </c>
       <c r="B8">
         <v>0.46987720987720999</v>
@@ -1135,8 +707,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
+      <c r="A9">
+        <v>11024</v>
       </c>
       <c r="B9">
         <v>0.30803582003581997</v>
@@ -1167,8 +739,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>20</v>
+      <c r="A10">
+        <v>11025</v>
       </c>
       <c r="B10">
         <v>0.54081096081096103</v>
@@ -1199,8 +771,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
+      <c r="A11">
+        <v>11031</v>
       </c>
       <c r="B11">
         <v>0.40061082461082498</v>
@@ -1231,8 +803,8 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
+      <c r="A12">
+        <v>11034</v>
       </c>
       <c r="B12">
         <v>0.375217647217647</v>
@@ -1263,8 +835,8 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
+      <c r="A13">
+        <v>11037</v>
       </c>
       <c r="B13">
         <v>0.36617391017390999</v>
@@ -1295,8 +867,8 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>24</v>
+      <c r="A14">
+        <v>11038</v>
       </c>
       <c r="B14">
         <v>0.38105223305223301</v>
@@ -1327,8 +899,8 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
+      <c r="A15">
+        <v>11042</v>
       </c>
       <c r="B15">
         <v>0.57606896406896402</v>
@@ -1359,8 +931,8 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
+      <c r="A16">
+        <v>11043</v>
       </c>
       <c r="B16">
         <v>0.43541411141411102</v>
@@ -1391,8 +963,8 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>27</v>
+      <c r="A17">
+        <v>11047</v>
       </c>
       <c r="B17">
         <v>0.45070285870285898</v>
@@ -1423,8 +995,8 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
+      <c r="A18">
+        <v>11050</v>
       </c>
       <c r="B18">
         <v>0.28242004242004198</v>
@@ -1455,8 +1027,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>29</v>
+      <c r="A19">
+        <v>11051</v>
       </c>
       <c r="B19">
         <v>0.32276186276186303</v>
@@ -1487,8 +1059,8 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>30</v>
+      <c r="A20">
+        <v>11053</v>
       </c>
       <c r="B20">
         <v>0.420217572217572</v>
@@ -1519,8 +1091,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
+      <c r="A21">
+        <v>11055</v>
       </c>
       <c r="B21">
         <v>0.303476055476055</v>
@@ -1551,8 +1123,8 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>32</v>
+      <c r="A22">
+        <v>11057</v>
       </c>
       <c r="B22">
         <v>0.27562639162639202</v>
@@ -1583,8 +1155,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>33</v>
+      <c r="A23">
+        <v>11060</v>
       </c>
       <c r="B23">
         <v>0.58991940191940195</v>
@@ -1615,8 +1187,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>34</v>
+      <c r="A24">
+        <v>11061</v>
       </c>
       <c r="B24">
         <v>0.431721275721276</v>
@@ -1647,8 +1219,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>35</v>
+      <c r="A25">
+        <v>11062</v>
       </c>
       <c r="B25">
         <v>0.46830270030269999</v>
@@ -1679,8 +1251,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>36</v>
+      <c r="A26">
+        <v>11065</v>
       </c>
       <c r="B26">
         <v>0.60597784197784199</v>
@@ -1711,8 +1283,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>37</v>
+      <c r="A27">
+        <v>11070</v>
       </c>
       <c r="B27">
         <v>0.50418933618933603</v>
@@ -1743,8 +1315,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>38</v>
+      <c r="A28">
+        <v>11072</v>
       </c>
       <c r="B28">
         <v>0.47820647820647799</v>
@@ -1775,8 +1347,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>39</v>
+      <c r="A29">
+        <v>11073</v>
       </c>
       <c r="B29">
         <v>0.40973320973320998</v>
@@ -1807,8 +1379,8 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>40</v>
+      <c r="A30">
+        <v>11074</v>
       </c>
       <c r="B30">
         <v>0.409347025347025</v>
@@ -1839,8 +1411,8 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>41</v>
+      <c r="A31">
+        <v>11078</v>
       </c>
       <c r="B31">
         <v>0.57514675114675096</v>
@@ -1871,8 +1443,8 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>42</v>
+      <c r="A32">
+        <v>11079</v>
       </c>
       <c r="B32">
         <v>0.35753434553434599</v>
@@ -1903,8 +1475,8 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>43</v>
+      <c r="A33">
+        <v>11085</v>
       </c>
       <c r="B33">
         <v>0.44659362259362301</v>
@@ -1935,8 +1507,8 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>44</v>
+      <c r="A34">
+        <v>11088</v>
       </c>
       <c r="B34">
         <v>0.26416645216645201</v>
@@ -1967,8 +1539,8 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>45</v>
+      <c r="A35">
+        <v>11089</v>
       </c>
       <c r="B35">
         <v>0.313733257733258</v>
@@ -1999,8 +1571,8 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>46</v>
+      <c r="A36">
+        <v>11091</v>
       </c>
       <c r="B36">
         <v>0.332121872121872</v>
@@ -2031,8 +1603,8 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>47</v>
+      <c r="A37">
+        <v>11092</v>
       </c>
       <c r="B37">
         <v>0.290871614871615</v>
@@ -2063,8 +1635,8 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>48</v>
+      <c r="A38">
+        <v>11093</v>
       </c>
       <c r="B38">
         <v>0.300033324033324</v>
@@ -2095,8 +1667,8 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>49</v>
+      <c r="A39">
+        <v>11097</v>
       </c>
       <c r="B39">
         <v>0.58189422589422601</v>
@@ -2127,8 +1699,8 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>50</v>
+      <c r="A40">
+        <v>11101</v>
       </c>
       <c r="B40">
         <v>0.43370463770463802</v>
@@ -2159,8 +1731,8 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>51</v>
+      <c r="A41">
+        <v>11102</v>
       </c>
       <c r="B41">
         <v>0.516379068379068</v>
@@ -2191,8 +1763,8 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>52</v>
+      <c r="A42">
+        <v>11103</v>
       </c>
       <c r="B42">
         <v>0.44144324144324099</v>
@@ -2223,8 +1795,8 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>53</v>
+      <c r="A43">
+        <v>11106</v>
       </c>
       <c r="B43">
         <v>0.358236538236538</v>
@@ -2255,8 +1827,8 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>54</v>
+      <c r="A44">
+        <v>11108</v>
       </c>
       <c r="B44">
         <v>0.41626583626583602</v>
@@ -2287,8 +1859,8 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>55</v>
+      <c r="A45">
+        <v>11110</v>
       </c>
       <c r="B45">
         <v>0.39898641898641901</v>
@@ -2319,8 +1891,8 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>56</v>
+      <c r="A46">
+        <v>11111</v>
       </c>
       <c r="B46">
         <v>0.64395957195957199</v>
@@ -2351,8 +1923,8 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>57</v>
+      <c r="A47">
+        <v>11113</v>
       </c>
       <c r="B47">
         <v>0.434432858432858</v>
@@ -2383,8 +1955,8 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>58</v>
+      <c r="A48">
+        <v>11115</v>
       </c>
       <c r="B48">
         <v>0.58521105321105304</v>
@@ -2415,8 +1987,8 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>59</v>
+      <c r="A49">
+        <v>11118</v>
       </c>
       <c r="B49">
         <v>0.318010386010386</v>
@@ -2447,8 +2019,8 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>60</v>
+      <c r="A50">
+        <v>11122</v>
       </c>
       <c r="B50">
         <v>0.52447828447828404</v>
@@ -2479,8 +2051,8 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>61</v>
+      <c r="A51">
+        <v>11127</v>
       </c>
       <c r="B51">
         <v>0.41940529140529098</v>
@@ -2511,8 +2083,8 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>62</v>
+      <c r="A52">
+        <v>11135</v>
       </c>
       <c r="B52">
         <v>0.20421438021437999</v>
@@ -2543,8 +2115,8 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>63</v>
+      <c r="A53">
+        <v>11141</v>
       </c>
       <c r="B53">
         <v>0.50752483552483596</v>
@@ -2575,8 +2147,8 @@
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>64</v>
+      <c r="A54">
+        <v>11145</v>
       </c>
       <c r="B54">
         <v>0.60855762855762896</v>
@@ -2607,8 +2179,8 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>65</v>
+      <c r="A55">
+        <v>11147</v>
       </c>
       <c r="B55">
         <v>0.40735442335442301</v>
@@ -2639,8 +2211,8 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>66</v>
+      <c r="A56">
+        <v>11157</v>
       </c>
       <c r="B56">
         <v>0.61943482343482403</v>
@@ -2671,8 +2243,8 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>67</v>
+      <c r="A57">
+        <v>11159</v>
       </c>
       <c r="B57">
         <v>0.51252574452574395</v>
@@ -2703,8 +2275,8 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>68</v>
+      <c r="A58">
+        <v>11166</v>
       </c>
       <c r="B58">
         <v>0.30888622488622502</v>
@@ -2735,8 +2307,8 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>69</v>
+      <c r="A59">
+        <v>11170</v>
       </c>
       <c r="B59">
         <v>0.32044282444282401</v>
@@ -2767,8 +2339,8 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>70</v>
+      <c r="A60">
+        <v>11171</v>
       </c>
       <c r="B60">
         <v>0.400565416565417</v>
@@ -2799,8 +2371,8 @@
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>71</v>
+      <c r="A61">
+        <v>11172</v>
       </c>
       <c r="B61">
         <v>0.38044474444474402</v>
@@ -2831,8 +2403,8 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>72</v>
+      <c r="A62">
+        <v>11175</v>
       </c>
       <c r="B62">
         <v>0.29186207186207203</v>
@@ -2863,8 +2435,8 @@
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>73</v>
+      <c r="A63">
+        <v>11179</v>
       </c>
       <c r="B63">
         <v>0.302740346740347</v>
@@ -2895,8 +2467,8 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>74</v>
+      <c r="A64">
+        <v>11180</v>
       </c>
       <c r="B64">
         <v>0.31712654912654897</v>
@@ -2927,8 +2499,8 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>75</v>
+      <c r="A65">
+        <v>11182</v>
       </c>
       <c r="B65">
         <v>0.45892243492243501</v>
@@ -2959,8 +2531,8 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>76</v>
+      <c r="A66">
+        <v>11197</v>
       </c>
       <c r="B66">
         <v>0.28773661173661202</v>
@@ -2991,8 +2563,8 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>77</v>
+      <c r="A67">
+        <v>11201</v>
       </c>
       <c r="B67">
         <v>0.43808314208314197</v>
@@ -3023,8 +2595,8 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>78</v>
+      <c r="A68">
+        <v>11207</v>
       </c>
       <c r="B68">
         <v>0.395379299379299</v>
@@ -3055,8 +2627,8 @@
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>79</v>
+      <c r="A69">
+        <v>11211</v>
       </c>
       <c r="B69">
         <v>0.47587551187551203</v>
@@ -3087,8 +2659,8 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>80</v>
+      <c r="A70">
+        <v>11213</v>
       </c>
       <c r="B70">
         <v>0.31537547137547101</v>
@@ -3119,8 +2691,8 @@
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>81</v>
+      <c r="A71">
+        <v>11214</v>
       </c>
       <c r="B71">
         <v>0.22393428793428799</v>
@@ -3151,8 +2723,8 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>82</v>
+      <c r="A72">
+        <v>11215</v>
       </c>
       <c r="B72">
         <v>0.21180078780078801</v>
@@ -3183,8 +2755,8 @@
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>83</v>
+      <c r="A73">
+        <v>11216</v>
       </c>
       <c r="B73">
         <v>0.50665079065079099</v>
@@ -3215,8 +2787,8 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>84</v>
+      <c r="A74">
+        <v>12008</v>
       </c>
       <c r="B74">
         <v>0.31156468756468803</v>
@@ -3247,8 +2819,8 @@
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>85</v>
+      <c r="A75">
+        <v>12010</v>
       </c>
       <c r="B75">
         <v>0.55855548655548704</v>
@@ -3279,8 +2851,8 @@
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>86</v>
+      <c r="A76">
+        <v>12011</v>
       </c>
       <c r="B76">
         <v>0.51605076005076</v>
@@ -3311,8 +2883,8 @@
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>87</v>
+      <c r="A77">
+        <v>12015</v>
       </c>
       <c r="B77">
         <v>0.55556099156099203</v>
@@ -3343,8 +2915,8 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>88</v>
+      <c r="A78">
+        <v>12017</v>
       </c>
       <c r="B78">
         <v>0.48915911715911697</v>
@@ -3375,8 +2947,8 @@
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>89</v>
+      <c r="A79">
+        <v>12028</v>
       </c>
       <c r="B79">
         <v>0.210751866751867</v>
@@ -3407,8 +2979,8 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>90</v>
+      <c r="A80">
+        <v>12035</v>
       </c>
       <c r="B80">
         <v>0.61653235653235705</v>
@@ -3439,8 +3011,8 @@
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>91</v>
+      <c r="A81">
+        <v>12052</v>
       </c>
       <c r="B81">
         <v>0.570914310914311</v>
@@ -3471,8 +3043,8 @@
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>92</v>
+      <c r="A82">
+        <v>12055</v>
       </c>
       <c r="B82">
         <v>0.53946412746412697</v>
@@ -3503,8 +3075,8 @@
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>93</v>
+      <c r="A83">
+        <v>12058</v>
       </c>
       <c r="B83">
         <v>0.217240465240465</v>
@@ -3535,8 +3107,8 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>94</v>
+      <c r="A84">
+        <v>12059</v>
       </c>
       <c r="B84">
         <v>0.16839188439188399</v>
@@ -3567,8 +3139,8 @@
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>95</v>
+      <c r="A85">
+        <v>12062</v>
       </c>
       <c r="B85">
         <v>0.210884814884815</v>
@@ -3599,8 +3171,8 @@
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>96</v>
+      <c r="A86">
+        <v>12075</v>
       </c>
       <c r="B86">
         <v>0.43311606111606099</v>
@@ -3631,8 +3203,8 @@
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>97</v>
+      <c r="A87">
+        <v>12076</v>
       </c>
       <c r="B87">
         <v>0.246102234102234</v>
@@ -3663,8 +3235,8 @@
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>98</v>
+      <c r="A88">
+        <v>12077</v>
       </c>
       <c r="B88">
         <v>0.12905150105150101</v>
@@ -3695,8 +3267,8 @@
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>99</v>
+      <c r="A89">
+        <v>12078</v>
       </c>
       <c r="B89">
         <v>0.24756934356934401</v>
@@ -3727,8 +3299,8 @@
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>100</v>
+      <c r="A90">
+        <v>12083</v>
       </c>
       <c r="B90">
         <v>0.32265475065475102</v>
@@ -3759,8 +3331,8 @@
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>101</v>
+      <c r="A91">
+        <v>12085</v>
       </c>
       <c r="B91">
         <v>0.15763923763923801</v>
@@ -3791,8 +3363,8 @@
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>102</v>
+      <c r="A92">
+        <v>12089</v>
       </c>
       <c r="B92">
         <v>0.238060858060858</v>
@@ -3823,8 +3395,8 @@
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>103</v>
+      <c r="A93">
+        <v>12096</v>
       </c>
       <c r="B93">
         <v>0.65683276483276498</v>
@@ -3855,8 +3427,8 @@
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>104</v>
+      <c r="A94">
+        <v>12099</v>
       </c>
       <c r="B94">
         <v>0.25275176475176497</v>
@@ -3887,8 +3459,8 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>105</v>
+      <c r="A95">
+        <v>12102</v>
       </c>
       <c r="B95">
         <v>0.15633782433782401</v>
@@ -3919,8 +3491,8 @@
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>106</v>
+      <c r="A96">
+        <v>12104</v>
       </c>
       <c r="B96">
         <v>0.27980283980283999</v>
@@ -3951,8 +3523,8 @@
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>107</v>
+      <c r="A97">
+        <v>12105</v>
       </c>
       <c r="B97">
         <v>0.18445770445770401</v>
@@ -3983,8 +3555,8 @@
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>108</v>
+      <c r="A98">
+        <v>12111</v>
       </c>
       <c r="B98">
         <v>0.43605840405840401</v>
@@ -4015,8 +3587,8 @@
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>109</v>
+      <c r="A99">
+        <v>12113</v>
       </c>
       <c r="B99">
         <v>0.43741201741201702</v>
@@ -4047,8 +3619,8 @@
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>110</v>
+      <c r="A100">
+        <v>12114</v>
       </c>
       <c r="B100">
         <v>0.36306708306708302</v>
@@ -4079,8 +3651,8 @@
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>111</v>
+      <c r="A101">
+        <v>12122</v>
       </c>
       <c r="B101">
         <v>0.31827229827229803</v>
@@ -4111,8 +3683,8 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>112</v>
+      <c r="A102">
+        <v>12127</v>
       </c>
       <c r="B102">
         <v>0.435692511692512</v>
@@ -4143,8 +3715,8 @@
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>113</v>
+      <c r="A103">
+        <v>12130</v>
       </c>
       <c r="B103">
         <v>0.237348285348285</v>
@@ -4175,8 +3747,8 @@
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>114</v>
+      <c r="A104">
+        <v>12137</v>
       </c>
       <c r="B104">
         <v>0.55730303330303299</v>
@@ -4207,8 +3779,8 @@
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>115</v>
+      <c r="A105">
+        <v>12138</v>
       </c>
       <c r="B105">
         <v>0.454897270897271</v>
@@ -4239,8 +3811,8 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>116</v>
+      <c r="A106">
+        <v>12152</v>
       </c>
       <c r="B106">
         <v>0.27034285834285798</v>
@@ -4271,8 +3843,8 @@
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>117</v>
+      <c r="A107">
+        <v>12157</v>
       </c>
       <c r="B107">
         <v>0.38719434319434298</v>
@@ -4303,8 +3875,8 @@
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>118</v>
+      <c r="A108">
+        <v>12160</v>
       </c>
       <c r="B108">
         <v>0.31009921009920999</v>
@@ -4335,8 +3907,8 @@
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>119</v>
+      <c r="A109">
+        <v>12165</v>
       </c>
       <c r="B109">
         <v>0.36204990204990201</v>
@@ -4367,8 +3939,8 @@
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>120</v>
+      <c r="A110">
+        <v>12169</v>
       </c>
       <c r="B110">
         <v>0.68710409110409099</v>
@@ -4399,8 +3971,8 @@
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>121</v>
+      <c r="A111">
+        <v>12172</v>
       </c>
       <c r="B111">
         <v>0.39490684690684702</v>
@@ -4431,8 +4003,8 @@
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>122</v>
+      <c r="A112">
+        <v>12174</v>
       </c>
       <c r="B112">
         <v>0.35893096693096699</v>
@@ -4463,8 +4035,8 @@
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>123</v>
+      <c r="A113">
+        <v>12177</v>
       </c>
       <c r="B113">
         <v>0.47722262122262099</v>
@@ -4495,8 +4067,8 @@
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>124</v>
+      <c r="A114">
+        <v>12183</v>
       </c>
       <c r="B114">
         <v>0.47327664527664498</v>
@@ -4527,8 +4099,8 @@
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>125</v>
+      <c r="A115">
+        <v>12186</v>
       </c>
       <c r="B115">
         <v>0.18172749772749799</v>
@@ -4559,8 +4131,8 @@
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>126</v>
+      <c r="A116">
+        <v>12188</v>
       </c>
       <c r="B116">
         <v>0.51263360063360097</v>
@@ -4591,8 +4163,8 @@
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>127</v>
+      <c r="A117">
+        <v>12189</v>
       </c>
       <c r="B117">
         <v>9.1080751080751102E-2</v>
@@ -4623,8 +4195,8 @@
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>128</v>
+      <c r="A118">
+        <v>12198</v>
       </c>
       <c r="B118">
         <v>0.51366843366843395</v>
@@ -4655,8 +4227,8 @@
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>129</v>
+      <c r="A119">
+        <v>12202</v>
       </c>
       <c r="B119">
         <v>0.36901611301611298</v>
@@ -4687,8 +4259,8 @@
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>130</v>
+      <c r="A120">
+        <v>12204</v>
       </c>
       <c r="B120">
         <v>0.173098457098457</v>
@@ -4719,8 +4291,8 @@
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>131</v>
+      <c r="A121">
+        <v>12216</v>
       </c>
       <c r="B121">
         <v>0.166750642750643</v>
@@ -4751,8 +4323,8 @@
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>132</v>
+      <c r="A122">
+        <v>12217</v>
       </c>
       <c r="B122">
         <v>0.49583155583155603</v>
@@ -4783,8 +4355,8 @@
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>133</v>
+      <c r="A123">
+        <v>12220</v>
       </c>
       <c r="B123">
         <v>0.38333611133611101</v>
@@ -4815,8 +4387,8 @@
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>134</v>
+      <c r="A124">
+        <v>12235</v>
       </c>
       <c r="B124">
         <v>0.621690165690166</v>
@@ -4847,8 +4419,8 @@
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>135</v>
+      <c r="A125">
+        <v>12236</v>
       </c>
       <c r="B125">
         <v>0.39076546276546298</v>
@@ -4879,8 +4451,8 @@
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>136</v>
+      <c r="A126">
+        <v>12238</v>
       </c>
       <c r="B126">
         <v>0.43072831072831103</v>
@@ -4911,8 +4483,8 @@
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>137</v>
+      <c r="A127">
+        <v>12242</v>
       </c>
       <c r="B127">
         <v>0.222631038631039</v>
@@ -4943,8 +4515,8 @@
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>138</v>
+      <c r="A128">
+        <v>12254</v>
       </c>
       <c r="B128">
         <v>0.38741240741240701</v>
@@ -4975,8 +4547,8 @@
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>139</v>
+      <c r="A129">
+        <v>12255</v>
       </c>
       <c r="B129">
         <v>0.59590831990832005</v>
@@ -5007,8 +4579,8 @@
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>140</v>
+      <c r="A130">
+        <v>12270</v>
       </c>
       <c r="B130">
         <v>0.61602379602379598</v>
@@ -5039,8 +4611,8 @@
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>141</v>
+      <c r="A131">
+        <v>12279</v>
       </c>
       <c r="B131">
         <v>0.443293151293151</v>
@@ -5071,8 +4643,8 @@
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>142</v>
+      <c r="A132">
+        <v>12281</v>
       </c>
       <c r="B132">
         <v>0.46623746223746199</v>
@@ -5103,8 +4675,8 @@
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>143</v>
+      <c r="A133">
+        <v>12283</v>
       </c>
       <c r="B133">
         <v>0.453586113586114</v>
@@ -5135,8 +4707,8 @@
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>144</v>
+      <c r="A134">
+        <v>12287</v>
       </c>
       <c r="B134">
         <v>0.28923854523854498</v>
@@ -5167,8 +4739,8 @@
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>145</v>
+      <c r="A135">
+        <v>12288</v>
       </c>
       <c r="B135">
         <v>0.39734180534180502</v>
@@ -5199,8 +4771,8 @@
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>146</v>
+      <c r="A136">
+        <v>12292</v>
       </c>
       <c r="B136">
         <v>0.53456549456549496</v>
@@ -5231,8 +4803,8 @@
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>147</v>
+      <c r="A137">
+        <v>12295</v>
       </c>
       <c r="B137">
         <v>0.33924248724248701</v>
@@ -5263,8 +4835,8 @@
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>148</v>
+      <c r="A138">
+        <v>12298</v>
       </c>
       <c r="B138">
         <v>0.49264856464856499</v>
@@ -5295,8 +4867,8 @@
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>149</v>
+      <c r="A139">
+        <v>12301</v>
       </c>
       <c r="B139">
         <v>0.56635019035018996</v>
@@ -5327,8 +4899,8 @@
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>150</v>
+      <c r="A140">
+        <v>12320</v>
       </c>
       <c r="B140">
         <v>0.110628998628999</v>
@@ -5359,8 +4931,8 @@
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>151</v>
+      <c r="A141">
+        <v>12334</v>
       </c>
       <c r="B141">
         <v>0.38620017820017799</v>
